--- a/registrations.xlsx
+++ b/registrations.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MSI\Desktop\New folder\SkillUp-Web\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MSI\Desktop\New folder\skillup-repo\SkillUp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A43A1D3-9C47-4BD5-B1F3-B63F58E5DEE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38BA0511-5415-4AC7-9E61-1EA63D443B39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,6 +17,10 @@
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
